--- a/Codelist Excel Files and Conversion Templates to XML/supportedStructureType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/supportedStructureType.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes naming what a rigid inclusion program supports - the load source the design is prepared for. Used for the value of the supportedStructureType property of diggs:RISystemBasis, which RI_Design_Parameter_Analysis.md Group A row 4 identifies as the master conditional a large part of the Design and Post-installation parameter groups key on: several other properties are meaningful only for an embankment or wall, others only for a slab or mat. The list is open.</t>
+          <t>Codes naming what a rigid inclusion program supports - the load source the design is prepared for. Used for the value of the supportedStructureType property of diggs:RIProgramBasis, which RI_Design_Parameter_Analysis.md Group A row 4 identifies as the master conditional a large part of the Design and Post-installation parameter groups key on: several other properties are meaningful only for an embankment or wall, others only for a slab or mat. The list is open.</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:supportedStructureType</t>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:supportedStructureType</t>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:supportedStructureType</t>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:supportedStructureType</t>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:supportedStructureType</t>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:supportedStructureType</t>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:supportedStructureType</t>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:supportedStructureType</t>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/supportedStructureType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/supportedStructureType.xlsx
@@ -1326,36 +1326,96 @@
         <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2948,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="13" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>wind_turbine</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Wind turbine foundation</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>A wind turbine foundation, typically a gravity base, carrying high overturning moment relative to its vertical load.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F10" s="13" t="n"/>
-      <c r="G10" s="9" t="n"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
         <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>pavement</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Pavement or apron</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>A pavement, hardstanding or airport apron - a large-area, relatively lightly loaded surface structure whose governing criterion is normally differential settlement.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="n"/>
-      <c r="G11" s="9" t="n"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
         <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2950,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="13" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>silo</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Silo</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>A silo or comparable tall storage structure imposing a high, concentrated and cyclically varying load on a small footprint.</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F12" s="13" t="n"/>
-      <c r="G12" s="9" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
@@ -1825,21 +1885,48 @@
         <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B10" s="20" t="n"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>wind_turbine</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" s="20" t="n"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>pavement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
         <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B12" s="20" t="n"/>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>silo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:supportedStructureType</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
